--- a/椙山改修/チェック/設計図_索引.xlsx
+++ b/椙山改修/チェック/設計図_索引.xlsx
@@ -75,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -87,9 +87,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,7 +474,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>日建設計「椙山女学園／星が丘キャンパス 大学会館食堂リニューアル工事（現場運用図）」No. J-241226-A　2026/03/27　A3 25頁（1頁＝表紙・図面リスト）</t>
+          <t>日建設計「椙山女学園／星が丘キャンパス 大学会館食堂リニューアル工事（現場運用図）」No. J-241226-A　2026/03/27　A3 25頁（1頁＝表紙・図面リスト）。機械は「電気・機械」シート</t>
         </is>
       </c>
     </row>
@@ -1286,47 +1283,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>設計図 索引（電気・機械）— 未着（表紙の図面リストから作成。図面が届いたら PDF頁を入れる）</t>
+          <t>設計図 索引（電気・機械）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>機械：日建設計 No. J-241226-A　2026/03/27　A1 8頁　椙山改修/参考/260327_設計図_機械A1.pdf（スキャン画像。文字検索不可）。電気は未着（表紙の図面リストから作成）。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>番号</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>図面番号</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>図面名</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>PDF頁</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>状態</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>主な内容</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>主に照合する施工図・製作図（目安）</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
@@ -1341,17 +1369,21 @@
           <t>01</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>電気設備特記仕様書（1）</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>未着</t>
         </is>
       </c>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1364,17 +1396,21 @@
           <t>02</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>電気設備特記仕様書（2）</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>未着</t>
         </is>
       </c>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1387,17 +1423,21 @@
           <t>03</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>電気設備概要、施工留意点、その他特記事項、凡例</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>未着</t>
         </is>
       </c>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1410,17 +1450,21 @@
           <t>04</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>外構設備図（既設図）（改修図）</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>未着</t>
         </is>
       </c>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1433,17 +1477,21 @@
           <t>05</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>変電設備図、幹線系統図（既設図）（改修図）</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>未着</t>
         </is>
       </c>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1456,17 +1504,21 @@
           <t>06</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>幹線・コンセント設備 凡例、地下1階平面図（既設図）</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>未着</t>
         </is>
       </c>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1479,17 +1531,21 @@
           <t>07</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>幹線・コンセント設備 凡例、地下1階平面図（改修図）</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>未着</t>
         </is>
       </c>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1502,17 +1558,21 @@
           <t>08</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>幹線・コンセント設備 凡例、1階平面図（既設図）（改修図）</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>未着</t>
         </is>
       </c>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1525,17 +1585,21 @@
           <t>09</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>分電盤注記、分電盤リスト</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>未着</t>
         </is>
       </c>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1548,17 +1612,21 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>照明器具姿図</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>未着</t>
         </is>
       </c>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1571,17 +1639,21 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>照明制御設備 システム概要、機器仕様、機器姿図、系統図（改修図）</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>未着</t>
         </is>
       </c>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1594,17 +1666,21 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>照明、誘導灯設備 凡例、1階平面図（既設図）（改修図）</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>未着</t>
         </is>
       </c>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1617,17 +1693,21 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>業務用兼用非常放送設備 システム図、機器姿図、系統図（既設図）（改修図）</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>未着</t>
         </is>
       </c>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1640,17 +1720,21 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>業務用兼用非常放送設備 凡例、1階平面図（既設図）（改修図）</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>未着</t>
         </is>
       </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1663,17 +1747,21 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>自動火災報知設備 系統図（既設図）（改修図）</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>未着</t>
         </is>
       </c>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1686,17 +1774,21 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>自動火災報知設備 1階平面図（既設図）（改修図）</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>未着</t>
         </is>
       </c>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1709,17 +1801,21 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>防火区画貫通処理要領図</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>未着</t>
         </is>
       </c>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1732,17 +1828,35 @@
           <t>01</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>機 01-01</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>機械設備特記仕様書（1）</t>
         </is>
       </c>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>未着</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>機械工事の仕様（材料・工法・試験）</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>全般（天井内・床下の設備との取合い）</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1755,17 +1869,35 @@
           <t>02</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>機 01-02</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>機械設備特記仕様書（2）</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>未着</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1778,17 +1910,35 @@
           <t>03</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>機 01-03</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>機械設備特記仕様書（3）</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>未着</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1801,17 +1951,35 @@
           <t>04</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>機 01-04</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>計画概要書、凡例、部分要領図</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>未着</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>計画概要、凡例、部分要領図</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>仕上-2、三友-18・19（チャンバーボックス）</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -1824,15 +1992,37 @@
           <t>05</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>機 02-01</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>空調設備 空調機器表、地下1階・1階空調配管平面図</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>未着</t>
+      <c r="E25" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>空調機器表、冷媒配管</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>仕上-2、三友-8・18・19、天井点検口（三和-5）</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>追変-機01 の印あり</t>
         </is>
       </c>
     </row>
@@ -1847,15 +2037,37 @@
           <t>06</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>機 03-01</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>空調設備 1階ダクト平面図</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>未着</t>
+      <c r="E26" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>1階ダクト・吹出口の配置（撤去・新設）</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>仕上-2、三友-8・15・18〜21、MIDIC-1、三和-5</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>追変-機01 の印あり</t>
         </is>
       </c>
     </row>
@@ -1870,17 +2082,35 @@
           <t>07</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>機 04-01</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>衛生設備 1階配管平面図</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>未着</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>1階の給排水配管</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>仕上-1、三友-16（ステンレスカウンター）、意 1-23 詳細19（手洗いカウンター）</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1893,15 +2123,37 @@
           <t>08</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>衛生設備 参考図 1階配管平面図</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>未着</t>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>機 05-01</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>衛生設備 参考図 1階配管平面図（図枠は B1階）</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>地下1階の配管（参考図）</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>図枠の名称は「参考図 B1階配管平面図」（表紙の図面リストは「1階」）</t>
         </is>
       </c>
     </row>

--- a/椙山改修/チェック/設計図_索引.xlsx
+++ b/椙山改修/チェック/設計図_索引.xlsx
@@ -1307,7 +1307,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>機械：日建設計 No. J-241226-A　2026/03/27　A1 8頁　椙山改修/参考/260327_設計図_機械A1.pdf（スキャン画像。文字検索不可）。電気は未着（表紙の図面リストから作成）。</t>
+          <t>機械：日建設計 No. J-241226-A　2026/03/27　A1 8頁　椙山改修/参考/260327_設計図_機械A1.pdf（スキャン画像。文字検索不可）。電気：同 No.　図枠の日付 2026/03/27（ファイル名の先頭は 260803）　A3 17頁　椙山改修/参考/260803_設計図_電気.pdf（スキャン画像）。図面名は表紙の図面リストと一致、追変の印なし。</t>
         </is>
       </c>
     </row>
@@ -1369,20 +1369,34 @@
           <t>01</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>電 -01</t>
+        </is>
+      </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
           <t>電気設備特記仕様書（1）</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n"/>
+      <c r="E4" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>未着</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>電気工事の仕様（材料・工法・試験）</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>全般（天井内・壁内の配線・ボックスとの取合い）</t>
+        </is>
+      </c>
       <c r="I4" s="5" t="n"/>
     </row>
     <row r="5">
@@ -1396,20 +1410,34 @@
           <t>02</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>電 -02</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
           <t>電気設備特記仕様書（2）</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n"/>
+      <c r="E5" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>未着</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
       <c r="I5" s="5" t="n"/>
     </row>
     <row r="6">
@@ -1423,20 +1451,34 @@
           <t>03</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>電 -03</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
           <t>電気設備概要、施工留意点、その他特記事項、凡例</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n"/>
+      <c r="E6" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>未着</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>電気設備の概要、施工上の留意点、凡例</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>全般</t>
+        </is>
+      </c>
       <c r="I6" s="5" t="n"/>
     </row>
     <row r="7">
@@ -1450,20 +1492,34 @@
           <t>04</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>電 -04</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
           <t>外構設備図（既設図）（改修図）</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n"/>
+      <c r="E7" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>未着</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>外構の電気設備（既設・改修）</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>参考（外構工事）</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="n"/>
     </row>
     <row r="8">
@@ -1477,20 +1533,34 @@
           <t>05</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>電 -05</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>変電設備図、幹線系統図（既設図）（改修図）</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n"/>
+      <c r="E8" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>未着</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>変電設備・幹線系統（既設・改修）</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
       <c r="I8" s="5" t="n"/>
     </row>
     <row r="9">
@@ -1504,20 +1574,34 @@
           <t>06</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>電 -06</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
           <t>幹線・コンセント設備 凡例、地下1階平面図（既設図）</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n"/>
+      <c r="E9" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>未着</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>地下1階の幹線・コンセント（既設）</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="n"/>
     </row>
     <row r="10">
@@ -1531,20 +1615,34 @@
           <t>07</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>電 -07</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
           <t>幹線・コンセント設備 凡例、地下1階平面図（改修図）</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n"/>
+      <c r="E10" s="4" t="n">
+        <v>7</v>
+      </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>未着</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>地下1階の幹線・コンセント（改修）</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
       <c r="I10" s="5" t="n"/>
     </row>
     <row r="11">
@@ -1558,20 +1656,34 @@
           <t>08</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n"/>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>電 -08</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
           <t>幹線・コンセント設備 凡例、1階平面図（既設図）（改修図）</t>
         </is>
       </c>
-      <c r="E11" s="4" t="n"/>
+      <c r="E11" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>未着</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>1階の幹線・コンセント（既設・改修）</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>仕上-1、三友-7・11・12・16（腰壁・カウンター内のコンセント）、MIDIC-3</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="n"/>
     </row>
     <row r="12">
@@ -1585,20 +1697,34 @@
           <t>09</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>電 -09</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
           <t>分電盤注記、分電盤リスト</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n"/>
+      <c r="E12" s="4" t="n">
+        <v>9</v>
+      </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>未着</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>分電盤の注記・リスト</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
       <c r="I12" s="5" t="n"/>
     </row>
     <row r="13">
@@ -1612,20 +1738,34 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n"/>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>電 -10</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
           <t>照明器具姿図</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n"/>
+      <c r="E13" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>未着</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>照明器具の姿図・仕様</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>仕上-2、三友-20・21（照明ボックス）、MIDIC-1、意 1-23 詳細08・13</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="n"/>
     </row>
     <row r="14">
@@ -1639,20 +1779,34 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>電 -11</t>
+        </is>
+      </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
           <t>照明制御設備 システム概要、機器仕様、機器姿図、系統図（改修図）</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n"/>
+      <c r="E14" s="4" t="n">
+        <v>11</v>
+      </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>未着</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>照明制御のシステム・機器・系統</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>参考（スイッチ類の位置は仕上-1・仕上-3）</t>
+        </is>
+      </c>
       <c r="I14" s="5" t="n"/>
     </row>
     <row r="15">
@@ -1666,20 +1820,34 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n"/>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>電 -12</t>
+        </is>
+      </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
           <t>照明、誘導灯設備 凡例、1階平面図（既設図）（改修図）</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n"/>
+      <c r="E15" s="4" t="n">
+        <v>12</v>
+      </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>未着</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>1階の照明・誘導灯の配置（既設・改修）</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>仕上-2、三友-8・15・20・21、MIDIC-1、三和-5</t>
+        </is>
+      </c>
       <c r="I15" s="5" t="n"/>
     </row>
     <row r="16">
@@ -1693,20 +1861,34 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>電 -13</t>
+        </is>
+      </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
           <t>業務用兼用非常放送設備 システム図、機器姿図、系統図（既設図）（改修図）</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n"/>
+      <c r="E16" s="4" t="n">
+        <v>13</v>
+      </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>未着</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>非常放送のシステム・機器・系統</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
       <c r="I16" s="5" t="n"/>
     </row>
     <row r="17">
@@ -1720,20 +1902,34 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n"/>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>電 -14</t>
+        </is>
+      </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
           <t>業務用兼用非常放送設備 凡例、1階平面図（既設図）（改修図）</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n"/>
+      <c r="E17" s="4" t="n">
+        <v>14</v>
+      </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>未着</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>1階の非常放送（スピーカー）の配置</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>仕上-2、MIDIC-1</t>
+        </is>
+      </c>
       <c r="I17" s="5" t="n"/>
     </row>
     <row r="18">
@@ -1747,20 +1943,34 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n"/>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>電 -15</t>
+        </is>
+      </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
           <t>自動火災報知設備 系統図（既設図）（改修図）</t>
         </is>
       </c>
-      <c r="E18" s="4" t="n"/>
+      <c r="E18" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>未着</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>自動火災報知設備の系統</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
       <c r="I18" s="5" t="n"/>
     </row>
     <row r="19">
@@ -1774,20 +1984,34 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n"/>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>電 -16</t>
+        </is>
+      </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
           <t>自動火災報知設備 1階平面図（既設図）（改修図）</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n"/>
+      <c r="E19" s="4" t="n">
+        <v>16</v>
+      </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>未着</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>1階の感知器の配置</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>仕上-2、三友-8、MIDIC-1</t>
+        </is>
+      </c>
       <c r="I19" s="5" t="n"/>
     </row>
     <row r="20">
@@ -1801,20 +2025,34 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n"/>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>電 -17</t>
+        </is>
+      </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
           <t>防火区画貫通処理要領図</t>
         </is>
       </c>
-      <c r="E20" s="4" t="n"/>
+      <c r="E20" s="4" t="n">
+        <v>17</v>
+      </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>未着</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+          <t>受領</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>防火区画の貫通処理の要領</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>仕上-1、躯体-1（区画貫通部）</t>
+        </is>
+      </c>
       <c r="I20" s="5" t="n"/>
     </row>
     <row r="21">

--- a/椙山改修/チェック/設計図_索引.xlsx
+++ b/椙山改修/チェック/設計図_索引.xlsx
@@ -1307,7 +1307,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>機械：日建設計 No. J-241226-A　2026/03/27　A1 8頁　椙山改修/参考/260327_設計図_機械A1.pdf（スキャン画像。文字検索不可）。電気：同 No.　図枠の日付 2026/03/27（ファイル名の先頭は 260803）　A3 17頁　椙山改修/参考/260803_設計図_電気.pdf（スキャン画像）。図面名は表紙の図面リストと一致、追変の印なし。</t>
+          <t>機械：日建設計 No. J-241226-A　2026/03/27　A1 8頁　椙山改修/参考/260327_設計図_機械A1.pdf（スキャン画像。文字検索不可）。電気：同 No.　図枠の日付 2026/03/27（ファイル名の 260803＝受領日、10/31 小山さん確認）　A3 17頁　椙山改修/参考/260803_設計図_電気.pdf（スキャン画像）。図面名は表紙の図面リストと一致、追変の印なし。</t>
         </is>
       </c>
     </row>

--- a/椙山改修/チェック/設計図_索引.xlsx
+++ b/椙山改修/チェック/設計図_索引.xlsx
@@ -9,10 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="意匠" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="電気・機械" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="既存躯体" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'意匠'!$A$6:$F$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'意匠'!$6:$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'既存躯体'!$A$7:$I$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'既存躯体'!$7:$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +457,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -1284,7 +1287,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
@@ -2398,4 +2401,936 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>既存躯体図など（作図資料）索引</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ファイル：椙山改修/参考/260925_既存躯体図.pdf（A3 19頁、eYACHO。PDFの題名「260925_2階天井・伏図作図資料」。ファイル名の 260925＝受領日と思われる（未確認））。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>中身は3種類：①1〜6頁＝今回の設計図（意匠、2026/03/27）に変更案を書き込んだもの ②7〜15頁＝既存の構造図（竣工図。70-83B132 椙山女学園大学大学会館他外構、図面の日付 昭和59(1984)/8/20、竣工 昭和60(1985)/9/30、清水建設一級建築士事務所）③16〜19頁＝平成27(2015)年の「大学会館東側食堂天井耐震化工事」の図面（70 15A017、工期 2015/8/11〜9/20）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>既存の構造図は全25枚（S-1〜S-25、7頁の目録）のうち S-4・6・7・9〜13 の8枚だけ。S-1 構造仕様表、S-3 杭伏図・基礎伏図、S-5 3階・屋根伏図、S-8 基礎・基礎梁リストなどは入っていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>手書き（ピンク）のメモがある頁は「メモ」欄に書いた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>PDF頁</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>図面番号</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>図面名</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>縮尺</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>図面の日付・版</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>主な内容</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>主に照合する施工図・製作図・計画書（目安）</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>メモ（図面上の手書きなど）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>変更案</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>内観パース（変更案）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>食堂内観のパースに変更案を色分け（天井／立上り／立上り1／立上り2）</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>仕上-2・3、三友-8・9・15</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>凡例「変更案」</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>設計図＋書込み</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>意 1-15</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>平面図（撤去・改修）</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>1/300</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>2026/03/27</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>平面図に変更案の範囲を書き込み（青＝撤去、赤＝改修）</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>仕上-1・4</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>設計図＋書込み</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>意 1-19</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>天井伏図（撤去・改修）</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>2026/03/27</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>天井伏図に変更案の範囲を書き込み</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>仕上-2、三友-8、MIDIC-1</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>設計図＋書込み</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>意 1-20</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>展開図1（撤去・改修）</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>2026/03/27</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>展開図に変更案（立上り）を書き込み</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>仕上-3、三友-9・15、MIDIC-1</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>設計図＋書込み</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>意 1-22</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>断面詳細図（撤去・改修）</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>2026/03/27</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>断面詳細に変更案を書き込み</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>三友-8・9・15、MIDIC-1</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>設計図＋書込み</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>意 1-16</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>平面詳細図（改修）・部分詳細図</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>1/100・図示</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>2026/03/27</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>平面詳細・部分詳細（書込みあり）</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>仕上-1、三友-7・11・12</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>既存構造図</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>（目録）</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>構造図 目録（S-1〜S-25）</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>竣工 1985/9/30</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>既存構造図の一覧（構造一般図 S-1〜14、構造詳細図 S-15〜23、構造計算書 S-24・25）</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1（ほかに要る図面を探すとき）</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>「既存S図」</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>既存構造図</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>S-4</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>1・2階床伏図</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>1984/8/20（竣工 1985/9/30）</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>1階・2階の床伏図（通り芯・柱・大梁・小梁・スラブの符号、床レベル）</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1、三友-7・8・9・11・24（下地鉄骨の取付け先）、計-4 あと施工アンカー</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>2階伏図の東側に丸印と「C3 G5 B5 CG1 CS2 S3」</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>既存構造図</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>S-6</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>軸組図</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>1984/8/20（竣工 1985/9/30）</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>軸組（階高・梁成・柱）</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1、仕上-3、三友-8・9（梁下・梁成の確認）</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>丸印あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>既存構造図</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>S-7</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>軸組図・外部階段伏図・軸組図</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>1984/8/20（竣工 1985/9/30）</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>軸組、外部階段の伏図</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1、仕上-3</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>丸印あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>既存構造図</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>S-9</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>柱リスト</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>1984/8/20（竣工 1985/9/30）</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>柱の断面・配筋</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1、三友-7・8・9・11・24（下地鉄骨の取付け先）、計-4 あと施工アンカー</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>丸印あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>既存構造図</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>S-10</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>大梁リスト</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>1984/8/20（竣工 1985/9/30）</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>大梁の断面・配筋</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1、三友-7・8・9・11・24（下地鉄骨の取付け先）、計-4 あと施工アンカー</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>丸印あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>既存構造図</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>S-11</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>床版リスト・小梁リスト・壁リスト・雑リスト</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>1:50・1:30</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>1984/8/20（竣工 1985/9/30）</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>スラブ厚・小梁・壁の断面・配筋</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1、三友-7・8・9・11・24（下地鉄骨の取付け先）、計-4 あと施工アンカー</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>丸印あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>既存構造図</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>S-12</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>鉄骨詳細図</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>1984/8/20（竣工 1985/9/30）</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>既存鉄骨の詳細</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1、三友-8・24</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>丸印あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>既存構造図</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>S-13</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>プレストレストコンクリート設計条件・PG1リスト 他</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>1:20・1:50</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>1984/8/20（竣工 1985/9/30）</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>PC梁（PG1）の設計条件・断面・緊張材</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1、計-4（PC梁へのアンカー・穴あけは不可の確認）、三友-8</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>「PC梁KTかな？要注意」</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>2015 耐震化</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>A-01</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>建物概要表</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>2015（耐震化工事）</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>2015 東側食堂天井耐震化工事の建物概要・工事項目（天井・照明LED化・スピーカー更新など）</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>仕上-2（既存天井の仕様）</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>「CADないのか？」、工期 H27/8/11〜9/20 に丸印</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>2015 耐震化</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>A-02</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>天井伏図・断面詳細図・展開図</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>1/100（A1）1/200（A3）</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>2015（耐震化工事）</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>2015 改修時の天井伏・天井断面詳細・展開</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>仕上-2・3・4、三友-8</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>2015 耐震化</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>M-1</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>空調設備 機器表・系統図・平面図</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>1/100（A1）1/200（A3）</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>2015（耐震化工事）</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>2015 改修時の空調</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>仕上-2（参考）</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>2015 耐震化</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>E-01</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>電灯・自火報・非常放送設備 平面図</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>1/100（A1）1/200（A3）</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>2015（耐震化工事）</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>2015 改修時の電灯・自火報・放送</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>仕上-2（参考）</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I26"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/椙山改修/チェック/設計図_索引.xlsx
+++ b/椙山改修/チェック/設計図_索引.xlsx
@@ -2433,7 +2433,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ファイル：椙山改修/参考/260925_既存躯体図.pdf（A3 19頁、eYACHO。PDFの題名「260925_2階天井・伏図作図資料」。ファイル名の 260925＝受領日と思われる（未確認））。</t>
+          <t>ファイル：椙山改修/参考/260925_既存躯体図.pdf（A3 19頁、eYACHO。PDFの題名「260925_2階天井・伏図作図資料」。ファイル名の 260925＝受領日、10/31 小山さん確認）。</t>
         </is>
       </c>
     </row>

--- a/椙山改修/チェック/設計図_索引.xlsx
+++ b/椙山改修/チェック/設計図_索引.xlsx
@@ -10,12 +10,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="意匠" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="電気・機械" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="既存躯体" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="既存意匠" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'意匠'!$A$6:$F$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'意匠'!$6:$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'既存躯体'!$A$7:$I$26</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'既存躯体'!$7:$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'既存意匠'!$A$7:$J$55</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'既存意匠'!$7:$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -47,7 +50,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +60,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -89,6 +97,12 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2410,7 +2424,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -3333,4 +3347,1997 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>既存竣工図（意匠）索引</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ファイル：椙山改修/参考/既存竣工図_意匠（S60大学会館他外構）.pdf（A3 47頁、スキャン画像）。綴り表：類別 A NO.4806、竣工 昭和60(1985)/10/31、工事名 70-83B132 椙山女学園大学大学会館他外構、清水建設一級建築士事務所。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>構成：1頁＝綴り表、2頁＝A-0 建物配置図・面積表、3〜13頁＝キャンパスヤード A-1〜11、14〜47頁＝大学会館 A-1〜35。図面番号は各頁右下の「竣工図 A○」の印（綴り表の番号）で照合した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>綴り表との食い違い：大学会館 A-26「正門」が入っていない（47頁＝綴り表46枚＋A-0 から1枚欠け）。A-27 歩道橋は図枠の番号が「A-28」に見える（印は A27）。A-28〜35 は図枠の番号が別系統（「－」や A-1〜4）なので、印の番号を使う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>★＝食堂の改修で特に見る図面。「今回の設計図」は設計図_索引の「意匠」シートの図面番号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>PDF頁</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>図面番号</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>図面名</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>縮尺</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>主な内容（食堂まわり）</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>今回の設計図との対応</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>主に照合する施工図・製作図（目安）</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>綴り表</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>綴り表（図面目録）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード A-1〜11、大学会館 A-1〜35 の目録</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>A-0</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>建物配置図・面積表</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>配置・面積</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>意 1-02</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>A-1</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>建物概要表</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>（外構工事の参考。一覧のみ）</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>外構工事の参考</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>A-2</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>外部・内部仕上表</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>（外構工事の参考。一覧のみ）</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>外構工事の参考</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>A-3</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>附近見取図・配置図</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>1:500</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>（外構工事の参考。一覧のみ）</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>外構工事の参考</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>A-4</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>1階平面図</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>（外構工事の参考。一覧のみ）</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>外構工事の参考</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>A-5</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>B1階平面図</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>（外構工事の参考。一覧のみ）</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>外構工事の参考</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>A-6</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>断面図・立面図</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>（外構工事の参考。一覧のみ）</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>外構工事の参考</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>A-7</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>矩計図</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>（外構工事の参考。一覧のみ）</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>外構工事の参考</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>A-8</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>スロープ部分平面図・断面図</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>1:100・1:50</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>（外構工事の参考。一覧のみ）</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>外構工事の参考</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>A-9</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>文学部庭</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>（外構工事の参考。一覧のみ）</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>外構工事の参考</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>A-10</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>建具表</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>（外構工事の参考。一覧のみ）</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>外構工事の参考</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>A-11</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>スタンド廻り詳細図</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>1:50・1:20</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>（外構工事の参考。一覧のみ）</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>外構工事の参考</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>A-1</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>建物概要表</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>建物概要</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>意 1-01</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>A-2</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>外部仕上表</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>外部仕上げ</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>意 1-14</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>A-3</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>配置図</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>1:500</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>配置</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>意 1-02</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>A-4</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>全体平均地盤面計算図</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>1:500</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>平均地盤面</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>A-5</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>日影図</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>1:500</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>日影</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>A-6</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>等時間日影図</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>1:500</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>日影</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>A-7</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>体育館・キャンパスヤード・大学会館（1棟）面積表</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>面積</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>A-8</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>1階平面図</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>1階全体の平面（食堂・厨房・ホール、外構を含む）</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>意 1-15・16</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>仕上-1・4、躯体-1</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>A-9</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>2階平面図</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>2階平面</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>仕上-2、三友-8</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>A-10</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>3階平面図・屋根伏図</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>3階・屋根</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>A-11</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>B1階平面図・求積図</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>地下1階・求積</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>A-12</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>断面図</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>建物の断面（階高・天井高）</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>意 1-17・22</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>仕上-3、三友-8・9</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>A-13</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>立面図</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>立面</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>意 1-17</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>A-14</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>矩計図</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>外壁まわりの断面詳細（階高・天井高・サッシ・庇・床仕上げ）</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>意 1-22</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>仕上-1・2・3、三友-8・9・11・12（窓際・腰壁）</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>A-15</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>コア棟・大学会館取合部 断面図・展開図</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>既存棟との取合い</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>A-16</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>階段詳細図</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>階段</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>A-17</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>1階平面図 天井伏図</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>食堂・厨房の平面（家具配置）と天井伏。食堂 CH=3,150、岩綿吸音板（PB下地）。照明・空調吹出口・点検口の位置</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>意 1-15・16・19</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>仕上-1・2・4、三友-8・15・18〜21、MIDIC-1、三和-5</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>天井の仕上げの文字はかすれて一部読みにくい</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>A-18</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>2階平面図 天井伏図</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>2階の平面・天井伏</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>A-19</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>展開図</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>各室の展開（食堂まわりのカウンター・建具を含む）</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>意 1-20・21</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>仕上-3、三友-12・16</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>A-20</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>平面詳細図（3階）</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>3階の詳細</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>A-21</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>展開図</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>展開</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>A-22</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>展開図（3F廊下）</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>3階廊下</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>A-23</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>天井伏図</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>（読み取れず）</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>天井伏</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>意 1-19</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>仕上-2</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>A-24</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>建具表（1）</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>既存建具の姿図・寸法・仕様</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>意 1-18</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>三和-1〜5、タジマ-1（既存建具の撤去・改修の範囲）</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>A-25</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>建具表（2）</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>既存建具の姿図・寸法・仕様</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>意 1-18</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>三和-1〜5、タジマ-1</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>A-26</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>正門</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>（PDFに無し）</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>綴り表にあるが入っていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>A-27</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>歩道橋</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>外構</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>外構工事の参考</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>図枠の番号は「A-28」に見える</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>A-28</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>B1階平面図（厨房詳細）</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>地下厨房</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>A-29</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>展開図（食堂）</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>食堂の展開（3枚のうち1枚目。窓・腰壁・カウンター・建具）</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>意 1-20・21</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>仕上-3、三友-9・11・12・13、MIDIC-1</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>図枠の番号は A-1（別系統）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>A-30</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>展開図（食堂）</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>食堂の展開（2枚目）</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>意 1-20・21</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>仕上-3、三友-7・9・11・15、MIDIC-1</t>
+        </is>
+      </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>図枠の番号は A-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>A-31</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>展開図（食堂）</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>食堂の展開（3枚目）</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>意 1-20・21</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>仕上-3、三友-12・16</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>図枠の番号は A-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>A-32</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>展開図（喫茶室）</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>喫茶室の展開・部分詳細</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr"/>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>（参考）</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>図枠の番号は A-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>A-33</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>敷地北西角改造図</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>外構</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>外構工事の参考</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>図枠の番号は A-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>A-34</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>平面図・断面図</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>（図面名の括弧書きは読み取れず）</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr"/>
+      <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>A-35</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>図書館前連絡階段 平面図・断面図</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>外構</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr"/>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>外構工事の参考</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:J55"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/椙山改修/チェック/設計図_索引.xlsx
+++ b/椙山改修/チェック/設計図_索引.xlsx
@@ -15,9 +15,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'意匠'!$A$6:$F$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'意匠'!$6:$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'既存躯体'!$A$7:$I$26</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'既存躯体'!$7:$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'既存意匠'!$A$7:$J$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'既存躯体'!$A$14:$K$57</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'既存躯体'!$14:$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'既存意匠'!$A$7:$L$57</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'既存意匠'!$7:$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -97,6 +97,10 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2423,927 +2427,2306 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:K57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>既存躯体図など（作図資料）索引</t>
+          <t>既存躯体図（構造竣工図・作図資料）索引</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ファイル：椙山改修/参考/260925_既存躯体図.pdf（A3 19頁、eYACHO。PDFの題名「260925_2階天井・伏図作図資料」。ファイル名の 260925＝受領日、10/31 小山さん確認）。</t>
+          <t>ファイル①＝椙山改修/参考/既存竣工図_構造（S60大学会館他外構）.pdf（A3 24頁）：構造竣工図の全体。類別 S NO.4806、竣工 昭和60(1985)/9/30、70-83B132 椙山女学園大学大学会館他外構、清水建設一級建築士事務所。1頁＝目録、2〜24頁＝S-1〜S-23（大学会館 S-1〜14、キャンパスヤード S-15〜21、スロープ廻り S-22、キソ変更リスト S-23）。S-24 構造計算書・S-25 監理記録は目録だけで、図面は無い。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>中身は3種類：①1〜6頁＝今回の設計図（意匠、2026/03/27）に変更案を書き込んだもの ②7〜15頁＝既存の構造図（竣工図。70-83B132 椙山女学園大学大学会館他外構、図面の日付 昭和59(1984)/8/20、竣工 昭和60(1985)/9/30、清水建設一級建築士事務所）③16〜19頁＝平成27(2015)年の「大学会館東側食堂天井耐震化工事」の図面（70 15A017、工期 2015/8/11〜9/20）。</t>
+          <t>ファイル②＝椙山改修/参考/260925_既存躯体図.pdf（A3 19頁、eYACHO。題名「260925_2階天井・伏図作図資料」。260925＝受領日、10/31 小山さん確認）：設計図に変更案を書き込んだもの、①の S-4・6・7・9〜13 の写し（手書きメモ入り）、2015 天井耐震化工事の図面。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>既存の構造図は全25枚（S-1〜S-25、7頁の目録）のうち S-4・6・7・9〜13 の8枚だけ。S-1 構造仕様表、S-3 杭伏図・基礎伏図、S-5 3階・屋根伏図、S-8 基礎・基礎梁リストなどは入っていない。</t>
+          <t>②の S-4〜S-13 は①と同じ原図（右下の「名古屋 3NN」の番号が同じ。図面の日付 59・8・20 も同じ）。違いはピンクの手書きメモと丸印だけ。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>手書き（ピンク）のメモがある頁は「メモ」欄に書いた。</t>
+          <t>★＝今回の改修（下地鉄骨・アンカー・天井）で特に見る図面。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>注意点（PC梁・あと施工アンカー）— 計-4 あと施工アンカー工事施工計画書、三友の下地鉄骨製作図のチェックで使う</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>① コンクリート強度（S-1）：躯体一般 Fc=225 kg/cm²（約22 N/mm²）、PC梁・スラブ・柱の一部 Fc=350 kg/cm²（約34 N/mm²。位置は伏図・軸組図に明示とある）、土間 180 kg/cm²（約18 N/mm²）。普通ポルトランドセメント、AE減水剤。→ あと施工アンカーの許容耐力は Fc=22 N/mm² で計算するのが安全側（取付け先が 350 の部材と確認できたものだけ 34 を使う）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>② 鉄筋（S-1）：D10・D13＝SD30（スラブ・壁・帯筋・あばら筋）、D16〜D25＝SD35（小梁・大梁・柱の主筋）。ガス圧接あり（D19 以上）。→ アンカーの穴あけは鉄筋探査をしてから。鉄筋を切らない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>③ PC梁（S-13）：ポストテンション方式、フルプレストレス（設計時の許容引張応力 0）、F28=350 kg/cm²。PC鋼材 9-12.7φ ストランド（SWPR7）、PG1 は⑤〜⑦通り間（スパン約 22 m）。鋼材は放物線状に配置され、中央付近では梁下端に近い。→ PC梁（PG1）には、下面・側面ともあと施工アンカー・穴あけを原則しない（PC鋼材を傷つけると梁の耐力に直結）。やむを得ない場合は監理者（構造：平山さん）と協議し、PC鋼材の位置を確認してから。②作図資料の S-13 には「PC梁KTかな？要注意」の手書きメモあり。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>④ PG1 がどの階・どの梁か（食堂の天井まわりかどうか）は、S-4・S-5 伏図と S-6・S-7 軸組図で、下地鉄骨・吊りボルトの取付け位置と照合して確認する（未確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>⑤ 既存躯体は昭和60年竣工（築40年）。アンカーの施工試験（引張試験）を計-4 で計画に入れること。2015 天井耐震化工事で既に打たれたアンカー・吊りボルトの位置（②の A-02）との干渉にも注意。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>ファイル</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>PDF頁</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>図面番号</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>図面名</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>縮尺</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>図面の日付・版</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>主な内容</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>主に照合する施工図・製作図・計画書（目安）</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>メモ（図面上の手書きなど）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>メモ（②との関係・手書きなど）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>（目録）</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>構造図 目録（S-1〜S-25）</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>竣工 60・9・30</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>構造一般図 S-1〜14、構造詳細図 S-15〜23、構造計算書 S-24・25 の一覧</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>目録の S-24・25 は図面なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>S-1</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>構造仕様表</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>58・3・25</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>ボーリング・基礎・コンクリート・鉄筋・鉄骨・試験の仕様。Fc=225（一般）／350（PC梁・スラブ・柱の一部）、鉄筋 SD30・SD35</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>計-4、三友の下地鉄骨（アンカー）、躯体-1</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>注意点①②</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>S-2</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>（鉄筋コンクリート造配筋標準図）</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>配筋の標準（定着・継手・開口補強など）</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>計-4（穴あけ・開口補強）</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>図枠の図面名は空欄。名称は目録から</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>S-3</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>杭伏図・基礎伏図</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>杭・基礎の配置</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1（参考）</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>②に無い</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>S-4</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>1・2階床伏図</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>1階・2階の床伏図（通り芯・柱・大梁・小梁・スラブの符号）</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>躯体-1、三友-7・8・9・11・24（下地鉄骨の取付け先）、計-4</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>②8頁と同じ原図</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>S-5</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>3階床伏図・屋根伏図</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>3階・屋根の伏図（食堂の上階・屋根の梁）</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>躯体-1、三友-8（吹抜け天井下地）</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>②に無い</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>S-6</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>軸組図</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>軸組（階高・梁成）</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>躯体-1、仕上-3、三友-8・9</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>②9頁と同じ原図</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>S-7</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>軸組図・外部階段伏図・軸組図</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>軸組・外部階段</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1、仕上-3</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>②10頁と同じ原図</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>S-8</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>基礎リスト・基礎梁リスト</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>基礎・基礎梁の断面</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1（参考）</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>②に無い</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>S-9</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>柱リスト</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>柱の断面・配筋</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>躯体-1、三友-7・8・9・11・24（下地鉄骨の取付け先）、計-4</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>②11頁と同じ原図</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>S-10</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>大梁リスト</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>大梁の断面・配筋</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>躯体-1、三友-7・8・9・11・24（下地鉄骨の取付け先）、計-4</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>②12頁と同じ原図</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>S-11</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>床版リスト・小梁リスト・壁リスト・雑リスト</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>1:50・1:30</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>スラブ厚・小梁・壁の断面・配筋</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>躯体-1、三友-7・8・9・11・24（下地鉄骨の取付け先）、計-4</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>②13頁と同じ原図</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>S-12</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>鉄骨詳細図</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>既存鉄骨の詳細</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1、三友-8・24</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>②14頁と同じ原図</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>S-13</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>プレストレストコンクリート設計条件・PG1リスト 他</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>1:20・1:50</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>PC梁 PG1（ポストテンション、9-12.7φ、⑤〜⑦通り）の設計条件・断面・PC鋼材の配置</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>躯体-1、計-4、三友-8</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>②15頁と同じ原図。注意点③</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>S-14</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>正面玄関アーチ・文学部側アーチ構造図</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>アーチの構造</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>（外構の参考）</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>②に無い</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>構造（ヤード）</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>S-15</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>構造仕様表（キャンパスヤード）</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>59・5・1</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤードの構造仕様</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>（外構の参考）</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>構造（ヤード）</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>S-16</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>（配筋標準図、キャンパスヤード）</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>59・5・1</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>（外構の参考）</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>図枠の図面名は空欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>構造（ヤード）</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>S-17</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>杭・基礎・キャンパスヤード伏図</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>59・5・1</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>（外構の参考）</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>構造（ヤード）</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>S-18</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>軸組図</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>59・5・1</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>（外構の参考）</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>構造（ヤード）</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>S-19</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>基礎・地中梁・柱・大梁リスト</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>59・5・1</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>（外構の参考）</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>構造（ヤード）</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>S-20</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>雑リスト</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>59・5・1</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>（外構の参考）</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>構造（ヤード）</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>S-21</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>鉄筋詳細図</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>1:30</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>59・5・1</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>（外構の参考）</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>S-22</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>スロープ廻り構造図</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>1:50・1:30</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>スロープの構造</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>（外構の参考）</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>①構造竣工図</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>S-23</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>キソ（基礎）変更リスト</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>基礎の変更</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1（参考）</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>図面名は読み取り</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>変更案</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>内観パース（変更案）</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>食堂内観のパースに変更案を色分け（天井／立上り／立上り1／立上り2）</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>仕上-2・3、三友-8・9・15</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>凡例「変更案」</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>設計図＋書込み</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>意 1-15</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>平面図（撤去・改修）</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>1/300</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>2026/03/27</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>平面図に変更案の範囲を書き込み（青＝撤去、赤＝改修）</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>平面図に変更案の範囲を書き込み</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>仕上-1・4</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="K40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>設計図＋書込み</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>意 1-19</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>天井伏図（撤去・改修）</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>2026/03/27</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>天井伏図に変更案の範囲を書き込み</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>仕上-2、三友-8、MIDIC-1</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="K41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>設計図＋書込み</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>意 1-20</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>展開図1（撤去・改修）</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>2026/03/27</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>展開図に変更案（立上り）を書き込み</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>仕上-3、三友-9・15、MIDIC-1</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="K42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>設計図＋書込み</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>意 1-22</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>断面詳細図（撤去・改修）</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>1/100</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>2026/03/27</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>断面詳細に変更案を書き込み</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>三友-8・9・15、MIDIC-1</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="K43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>設計図＋書込み</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>意 1-16</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>平面詳細図（改修）・部分詳細図</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>1/100・図示</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>2026/03/27</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>平面詳細・部分詳細（書込みあり）</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>仕上-1、三友-7・11・12</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="K44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>既存構造図</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>構造（写し）</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>（目録）</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>構造図 目録（S-1〜S-25）</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>構造図 目録</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>竣工 1985/9/30</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>既存構造図の一覧（構造一般図 S-1〜14、構造詳細図 S-15〜23、構造計算書 S-24・25）</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>躯体-1（ほかに要る図面を探すとき）</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>竣工 60・9・30</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>①1頁と同じ</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr"/>
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>「既存S図」</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>既存構造図</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>構造（写し）</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>S-4</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="E46" s="9" t="inlineStr">
         <is>
           <t>1・2階床伏図</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t>1:200</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>1984/8/20（竣工 1985/9/30）</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>1階・2階の床伏図（通り芯・柱・大梁・小梁・スラブの符号、床レベル）</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>躯体-1、三友-7・8・9・11・24（下地鉄骨の取付け先）、計-4 あと施工アンカー</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>①5頁と同じ原図</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>躯体-1、三友-7・8・9・11・24（下地鉄骨の取付け先）、計-4</t>
+        </is>
+      </c>
+      <c r="K46" s="9" t="inlineStr">
         <is>
           <t>2階伏図の東側に丸印と「C3 G5 B5 CG1 CS2 S3」</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>既存構造図</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>構造（写し）</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>S-6</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>軸組図</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>1:200</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>1984/8/20（竣工 1985/9/30）</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>軸組（階高・梁成・柱）</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>躯体-1、仕上-3、三友-8・9（梁下・梁成の確認）</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>①7頁と同じ原図</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>丸印あり</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>既存構造図</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>構造（写し）</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>S-7</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>軸組図・外部階段伏図・軸組図</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>1:200</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>1984/8/20（竣工 1985/9/30）</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>軸組、外部階段の伏図</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>躯体-1、仕上-3</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>①8頁と同じ原図</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
         <is>
           <t>丸印あり</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>既存構造図</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>構造（写し）</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>S-9</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>柱リスト</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>1:50</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>1984/8/20（竣工 1985/9/30）</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>柱の断面・配筋</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>躯体-1、三友-7・8・9・11・24（下地鉄骨の取付け先）、計-4 あと施工アンカー</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>①10頁と同じ原図</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>丸印あり</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>既存構造図</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>構造（写し）</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>S-10</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>大梁リスト</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>1:50</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>1984/8/20（竣工 1985/9/30）</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>大梁の断面・配筋</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>躯体-1、三友-7・8・9・11・24（下地鉄骨の取付け先）、計-4 あと施工アンカー</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>①11頁と同じ原図</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
         <is>
           <t>丸印あり</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>既存構造図</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>構造（写し）</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>S-11</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>床版リスト・小梁リスト・壁リスト・雑リスト</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>1:50・1:30</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>1984/8/20（竣工 1985/9/30）</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>スラブ厚・小梁・壁の断面・配筋</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>躯体-1、三友-7・8・9・11・24（下地鉄骨の取付け先）、計-4 あと施工アンカー</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>①12頁と同じ原図</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
         <is>
           <t>丸印あり</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>既存構造図</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>構造（写し）</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>S-12</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>鉄骨詳細図</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>1:50</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>1984/8/20（竣工 1985/9/30）</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>既存鉄骨の詳細</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>躯体-1、三友-8・24</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>①13頁と同じ原図</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>躯体-1</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>丸印あり</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>既存構造図</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>構造（写し）</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>S-13</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="E53" s="9" t="inlineStr">
         <is>
           <t>プレストレストコンクリート設計条件・PG1リスト 他</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="F53" s="8" t="inlineStr">
         <is>
           <t>1:20・1:50</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>1984/8/20（竣工 1985/9/30）</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>PC梁（PG1）の設計条件・断面・緊張材</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>躯体-1、計-4（PC梁へのアンカー・穴あけは不可の確認）、三友-8</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>59・8・20（竣工 60・9・30）</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>①14頁と同じ原図</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>計-4</t>
+        </is>
+      </c>
+      <c r="K53" s="9" t="inlineStr">
         <is>
           <t>「PC梁KTかな？要注意」</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>2015 耐震化</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>A-01</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>建物概要表</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>2015（耐震化工事）</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>2015 東側食堂天井耐震化工事の建物概要・工事項目（天井・照明LED化・スピーカー更新など）</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>仕上-2（既存天井の仕様）</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>「CADないのか？」、工期 H27/8/11〜9/20 に丸印</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>2015 耐震化</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>A-02</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>天井伏図・断面詳細図・展開図</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="F55" s="8" t="inlineStr">
         <is>
           <t>1/100（A1）1/200（A3）</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>2015（耐震化工事）</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>2015 改修時の天井伏・天井断面詳細・展開</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>仕上-2・3・4、三友-8</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>2015 改修時の天井伏・天井断面詳細・展開（既存の天井下地・吊りボルト）</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>仕上-2・3・4、三友-8、計-4</t>
+        </is>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>注意点⑤</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>2015 耐震化</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>M-1</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>空調設備 機器表・系統図・平面図</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>1/100（A1）1/200（A3）</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>2015（耐震化工事）</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>2015 改修時の空調</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>仕上-2（参考）</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="K56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>②作図資料</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>2015 耐震化</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>E-01</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>電灯・自火報・非常放送設備 平面図</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>1/100（A1）1/200（A3）</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>2015（耐震化工事）</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>2015 改修時の電灯・自火報・放送</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="J57" s="5" t="inlineStr">
         <is>
           <t>仕上-2（参考）</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr"/>
+      <c r="K57" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:I26"/>
+  <autoFilter ref="A14:K57"/>
+  <mergeCells count="5">
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A11:J11"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3355,19 +4738,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3380,1963 +4765,2359 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ファイル：椙山改修/参考/既存竣工図_意匠（S60大学会館他外構）.pdf（A3 47頁、スキャン画像）。綴り表：類別 A NO.4806、竣工 昭和60(1985)/10/31、工事名 70-83B132 椙山女学園大学大学会館他外構、清水建設一級建築士事務所。</t>
+          <t>ファイル①＝椙山改修/参考/既存竣工図_意匠（S60大学会館他外構）.pdf（A3 47頁、スキャン画像）。綴り表：類別 A NO.4806、竣工 昭和60(1985)/10/31、工事名 70-83B132 椙山女学園大学大学会館他外構、清水建設一級建築士事務所。1頁＝綴り表、2頁＝A-0、3〜13頁＝キャンパスヤード A-1〜11、14〜47頁＝大学会館 A-1〜35（A-26 正門を除く）。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>構成：1頁＝綴り表、2頁＝A-0 建物配置図・面積表、3〜13頁＝キャンパスヤード A-1〜11、14〜47頁＝大学会館 A-1〜35。図面番号は各頁右下の「竣工図 A○」の印（綴り表の番号）で照合した。</t>
+          <t>ファイル②＝椙山改修/参考/既存竣工図_意匠その2（配置図・正門）.pdf（3頁）：同じ NO.4806 の追加分。1頁＝竣工原図登録表紙、2頁＝A-3 配置図（59・6・5、1:500）、3頁＝A-26 正門（60・7・23、1/50）。→ ①に無かった A-26 正門はここにある。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>綴り表との食い違い：大学会館 A-26「正門」が入っていない（47頁＝綴り表46枚＋A-0 から1枚欠け）。A-27 歩道橋は図枠の番号が「A-28」に見える（印は A27）。A-28〜35 は図枠の番号が別系統（「－」や A-1〜4）なので、印の番号を使う。</t>
+          <t>図面番号は各頁右下の「竣工図 A○」の印（綴り表の番号）で照合した。A-27 歩道橋は図枠の番号が「A-28」に見える（印は A27）。A-28〜35 は図枠の番号が別系統（「－」や A-1〜4）なので、印の番号を使う。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>★＝食堂の改修で特に見る図面。「今回の設計図」は設計図_索引の「意匠」シートの図面番号。</t>
+          <t>★＝食堂の改修で特に見る図面。「今回の設計図」は「意匠」シートの図面番号。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>ファイル</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
           <t>PDF頁</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>図面番号</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>図面名</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>縮尺</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>図面の日付</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>主な内容（食堂まわり）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>今回の設計図との対応</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>主に照合する施工図・製作図（目安）</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>メモ</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>綴り表</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>綴り表（図面目録）</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>キャンパスヤード A-1〜11、大学会館 A-1〜35 の目録</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>A-0</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>建物配置図・面積表</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>配置・面積</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>意 1-02</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>キャンパスヤード</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>A-1</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>建物概要表</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>（外構工事の参考。一覧のみ）</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>外構工事の参考</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>キャンパスヤード</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>A-2</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>外部・内部仕上表</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>（外構工事の参考。一覧のみ）</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>外構工事の参考</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>キャンパスヤード</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>A-3</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>附近見取図・配置図</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1:500</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>（外構工事の参考。一覧のみ）</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>外構工事の参考</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>キャンパスヤード</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>A-4</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>1階平面図</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1:200</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>（外構工事の参考。一覧のみ）</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>外構工事の参考</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>キャンパスヤード</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>A-5</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>B1階平面図</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1:200</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>（外構工事の参考。一覧のみ）</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>外構工事の参考</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>キャンパスヤード</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>A-6</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>断面図・立面図</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1:200</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>（外構工事の参考。一覧のみ）</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>外構工事の参考</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>キャンパスヤード</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>A-7</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>矩計図</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1:50</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>（外構工事の参考。一覧のみ）</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>外構工事の参考</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>キャンパスヤード</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>A-8</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>スロープ部分平面図・断面図</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1:100・1:50</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>（外構工事の参考。一覧のみ）</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>外構工事の参考</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>キャンパスヤード</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>A-9</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>文学部庭</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>1:100</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>（外構工事の参考。一覧のみ）</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>外構工事の参考</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>キャンパスヤード</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>A-10</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>建具表</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>1:100</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>（外構工事の参考。一覧のみ）</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>外構工事の参考</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>キャンパスヤード</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>A-11</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>スタンド廻り詳細図</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>1:50・1:20</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>（外構工事の参考。一覧のみ）</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>外構工事の参考</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>A-1</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>建物概要表</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>建物概要</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>意 1-01</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>A-2</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>外部仕上表</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>外部仕上げ</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>意 1-14</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>A-3</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>配置図</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>1:500</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>配置</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>意 1-02</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>②2頁に別版（59・6・5）あり</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>A-4</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>全体平均地盤面計算図</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>1:500</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>平均地盤面</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>A-5</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>日影図</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>1:500</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>日影</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>A-6</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>等時間日影図</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>1:500</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>日影</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>A-7</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>体育館・キャンパスヤード・大学会館（1棟）面積表</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>面積</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>A-8</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>1階平面図</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>1:200</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr"/>
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>1階全体の平面（食堂・厨房・ホール、外構を含む）</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>意 1-15・16</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="K28" s="9" t="inlineStr">
         <is>
           <t>仕上-1・4、躯体-1</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr"/>
+      <c r="L28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>A-9</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>2階平面図</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>1:200</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>2階平面</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>仕上-2、三友-8</t>
-        </is>
-      </c>
       <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>A-10</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>3階平面図・屋根伏図</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>1:200</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>3階・屋根</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>A-11</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>B1階平面図・求積図</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>1:200</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>地下1階・求積</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="n">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>A-12</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>断面図</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>1:200</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>建物の断面（階高・天井高）</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>意 1-17・22</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="K32" s="9" t="inlineStr">
         <is>
           <t>仕上-3、三友-8・9</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr"/>
+      <c r="L32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>A-13</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>立面図</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>1:200</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>立面</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>意 1-17</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="n">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>A-14</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>矩計図</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>1:50</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr"/>
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr">
         <is>
           <t>外壁まわりの断面詳細（階高・天井高・サッシ・庇・床仕上げ）</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>意 1-22</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="K34" s="9" t="inlineStr">
         <is>
           <t>仕上-1・2・3、三友-8・9・11・12（窓際・腰壁）</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr"/>
+      <c r="L34" s="9" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>A-15</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>コア棟・大学会館取合部 断面図・展開図</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>1:50</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>既存棟との取合い</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>A-16</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>階段詳細図</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>1:50</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>階段</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="n">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>A-17</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>1階平面図 天井伏図</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>1:100</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
         <is>
           <t>食堂・厨房の平面（家具配置）と天井伏。食堂 CH=3,150、岩綿吸音板（PB下地）。照明・空調吹出口・点検口の位置</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>意 1-15・16・19</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="K37" s="9" t="inlineStr">
         <is>
           <t>仕上-1・2・4、三友-8・15・18〜21、MIDIC-1、三和-5</t>
         </is>
       </c>
-      <c r="J37" s="7" t="inlineStr">
+      <c r="L37" s="9" t="inlineStr">
         <is>
           <t>天井の仕上げの文字はかすれて一部読みにくい</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>A-18</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>2階平面図 天井伏図</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>1:100</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>2階の平面・天井伏</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="n">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>A-19</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>展開図</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>1:100</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr"/>
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>各室の展開（食堂まわりのカウンター・建具を含む）</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="J39" s="9" t="inlineStr">
         <is>
           <t>意 1-20・21</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="K39" s="9" t="inlineStr">
         <is>
           <t>仕上-3、三友-12・16</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr"/>
+      <c r="L39" s="9" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>A-20</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>平面詳細図（3階）</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>1:50</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>3階の詳細</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>A-21</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>展開図</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>1:50</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>展開</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
+      <c r="K41" s="5" t="inlineStr"/>
+      <c r="L41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>A-22</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>展開図（3F廊下）</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>1:100</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>3階廊下</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr"/>
+      <c r="L42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>A-23</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>天井伏図</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>（読み取れず）</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>天井伏</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>意 1-19</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>仕上-2</t>
         </is>
       </c>
-      <c r="J43" s="5" t="inlineStr"/>
+      <c r="L43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="n">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>A-24</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>建具表（1）</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>1:100</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr"/>
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="I44" s="9" t="inlineStr">
         <is>
           <t>既存建具の姿図・寸法・仕様</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>意 1-18</t>
         </is>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="K44" s="9" t="inlineStr">
         <is>
           <t>三和-1〜5、タジマ-1（既存建具の撤去・改修の範囲）</t>
         </is>
       </c>
-      <c r="J44" s="7" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="n">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>A-25</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>建具表（2）</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t>1:100</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>既存建具の姿図・寸法・仕様</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>意 1-18</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="K45" s="9" t="inlineStr">
         <is>
           <t>三和-1〜5、タジマ-1</t>
         </is>
       </c>
-      <c r="J45" s="7" t="inlineStr"/>
+      <c r="L45" s="9" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
+          <t>②その2</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>A-26</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>正門</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>60・7・23</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>正門（60・7・23）</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>外構工事の参考</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>②3頁</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>A-27</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>歩道橋</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>外構</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr"/>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>外構工事の参考</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>図枠の番号は「A-28」に見える</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>A-28</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>B1階平面図（厨房詳細）</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>地下厨房</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr"/>
+      <c r="K48" s="5" t="inlineStr"/>
+      <c r="L48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>A-29</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>展開図（食堂）</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr"/>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>食堂の展開（3枚のうち1枚目。窓・腰壁・カウンター・建具）</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>意 1-20・21</t>
+        </is>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>仕上-3、三友-9・11・12・13、MIDIC-1</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>図枠の番号は A-1（別系統）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>A-30</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>展開図（食堂）</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr"/>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>食堂の展開（2枚目）</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>意 1-20・21</t>
+        </is>
+      </c>
+      <c r="K50" s="9" t="inlineStr">
+        <is>
+          <t>仕上-3、三友-7・9・11・15、MIDIC-1</t>
+        </is>
+      </c>
+      <c r="L50" s="9" t="inlineStr">
+        <is>
+          <t>図枠の番号は A-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>A-31</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>展開図（食堂）</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>食堂の展開（3枚目）</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>意 1-20・21</t>
+        </is>
+      </c>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>仕上-3、三友-12・16</t>
+        </is>
+      </c>
+      <c r="L51" s="9" t="inlineStr">
+        <is>
+          <t>図枠の番号は A-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>A-32</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>展開図（喫茶室）</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>喫茶室の展開・部分詳細</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr"/>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>（参考）</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>図枠の番号は A-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>A-33</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>敷地北西角改造図</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>外構</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr"/>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>外構工事の参考</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>図枠の番号は A-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>A-34</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>平面図・断面図</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>（図面名の括弧書きは読み取れず）</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr"/>
+      <c r="K54" s="5" t="inlineStr"/>
+      <c r="L54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>①意匠竣工図</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>A-35</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>図書館前連絡階段 平面図・断面図</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>外構</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr"/>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>外構工事の参考</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>②その2</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>表紙</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
           <t>－</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>竣工原図登録表紙</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>NO.4806 の追加登録分（A-3 配置図、A-26 正門）</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr"/>
+      <c r="K56" s="5" t="inlineStr"/>
+      <c r="L56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>②その2</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>大学会館</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>A-26</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>正門</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>（PDFに無し）</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>綴り表にあるが入っていない</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>大学会館</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>A-27</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>歩道橋</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>1:100</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr"/>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>外構</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>A-3</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>配置図（別版）</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>1:500</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>59・6・5</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>配置（①16頁の A-3 とは別の版）</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>意 1-02</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
         <is>
           <t>外構工事の参考</t>
         </is>
       </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>図枠の番号は「A-28」に見える</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>大学会館</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>A-28</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>B1階平面図（厨房詳細）</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>1:200</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr"/>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>地下厨房</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>大学会館</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>A-29</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>展開図（食堂）</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>1:50</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>食堂の展開（3枚のうち1枚目。窓・腰壁・カウンター・建具）</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>意 1-20・21</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>仕上-3、三友-9・11・12・13、MIDIC-1</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>図枠の番号は A-1（別系統）</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>大学会館</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>A-30</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>展開図（食堂）</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>1:50</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>食堂の展開（2枚目）</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>意 1-20・21</t>
-        </is>
-      </c>
-      <c r="I50" s="7" t="inlineStr">
-        <is>
-          <t>仕上-3、三友-7・9・11・15、MIDIC-1</t>
-        </is>
-      </c>
-      <c r="J50" s="7" t="inlineStr">
-        <is>
-          <t>図枠の番号は A-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>大学会館</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>A-31</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>展開図（食堂）</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>1:50</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>食堂の展開（3枚目）</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>意 1-20・21</t>
-        </is>
-      </c>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>仕上-3、三友-12・16</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="inlineStr">
-        <is>
-          <t>図枠の番号は A-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>大学会館</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>A-32</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>展開図（喫茶室）</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>1:50</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>喫茶室の展開・部分詳細</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>（参考）</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>図枠の番号は A-4</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>大学会館</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>A-33</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>敷地北西角改造図</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>1:100</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>外構</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>外構工事の参考</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>図枠の番号は A-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>大学会館</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>A-34</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>平面図・断面図</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>1:50</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr"/>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>（図面名の括弧書きは読み取れず）</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>大学会館</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>A-35</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>図書館前連絡階段 平面図・断面図</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>1:50</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr"/>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>外構</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>外構工事の参考</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr"/>
+      <c r="L57" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:J55"/>
+  <autoFilter ref="A7:L57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/椙山改修/チェック/設計図_索引.xlsx
+++ b/椙山改修/チェック/設計図_索引.xlsx
@@ -11,6 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="電気・機械" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="既存躯体" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="既存意匠" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="既存設備" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="既存2015天井耐震化" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'意匠'!$A$6:$F$31</definedName>
@@ -19,6 +21,10 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'既存躯体'!$14:$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'既存意匠'!$A$7:$L$57</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'既存意匠'!$7:$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'既存設備'!$A$6:$J$69</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'既存設備'!$6:$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'既存2015天井耐震化'!$A$14:$F$37</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'既存2015天井耐震化'!$14:$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2502,14 +2508,14 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>③ PC梁（S-13）：ポストテンション方式、フルプレストレス（設計時の許容引張応力 0）、F28=350 kg/cm²。PC鋼材 9-12.7φ ストランド（SWPR7）、PG1 は⑤〜⑦通り間（スパン約 22 m）。鋼材は放物線状に配置され、中央付近では梁下端に近い。→ PC梁（PG1）には、下面・側面ともあと施工アンカー・穴あけを原則しない（PC鋼材を傷つけると梁の耐力に直結）。やむを得ない場合は監理者（構造：平山さん）と協議し、PC鋼材の位置を確認してから。②作図資料の S-13 には「PC梁KTかな？要注意」の手書きメモあり。</t>
+          <t>③ PC梁（S-13）：ポストテンション方式、フルプレストレス（設計時の許容引張応力 0）、F28=350 kg/cm²。PC鋼材 9-12.7φ ストランド（SWPR7）、PG1 は③〜⑦通り間（スパン 22.0 m、定着部は M 通り側）。鋼材は放物線状に配置され、中央付近では梁下端に近い。→ PC梁（PG1）には、下面・側面ともあと施工アンカー・穴あけを原則しない（PC鋼材を傷つけると梁の耐力に直結）。やむを得ない場合は監理者（構造：平山さん）と協議し、PC鋼材の位置を確認してから。②作図資料の S-13 には「PC梁KTかな？要注意」の手書きメモあり。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>④ PG1 がどの階・どの梁か（食堂の天井まわりかどうか）は、S-4・S-5 伏図と S-6・S-7 軸組図で、下地鉄骨・吊りボルトの取付け位置と照合して確認する（未確認）。</t>
+          <t>④ PG1 の位置：2015 天井耐震化工事の S-1（既存3階床梁伏図）では、東側食堂（⑤〜⑦×K〜P、天井高 CH=7,700）の上は3階床梁（3G1 450×1100 など）で、柱は2階までと注記されている。食堂の上の3階床梁が PC の長スパン梁（PG1）である可能性が高い（S-5 3階床伏図で要確認）。2015 の天井下地（ブドウ棚）は、この3階梁の側面に B.PL＋エポキシ樹脂アンカー 2-M16 で取り付けてあり、特記に「大梁のスターラップを切断しないよう探査のうえ施工」とある。今回の三友-8・9・20・21・MIDIC-1 の取付けも同じ梁になるので、PC鋼材・既存アンカーの位置に特に注意。</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3315,7 @@
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>PC梁 PG1（ポストテンション、9-12.7φ、⑤〜⑦通り）の設計条件・断面・PC鋼材の配置</t>
+          <t>PC梁 PG1（ポストテンション、9-12.7φ、③〜⑦通り 22.0 m）の設計条件・断面・PC鋼材の配置</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
@@ -7121,4 +7127,3498 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>既存竣工図（機械・電気）索引</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>機械＝椙山改修/参考/既存竣工図_機械（S60大学会館他外構）.pdf（A3 28頁）：類別 M NO.4806、M1〜M26（川崎設備工業）。1頁＝目録（「M1〜M26」とだけ記載）、2〜27頁＝M1〜M26、28頁＝返却コーナー改造プラン（61・11・1、後の改造）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>電気＝椙山改修/参考/既存竣工図_電気（S60大学会館他外構）.pdf（A3 35頁）：類別 E NO.4806、竣工 60年9月。1頁＝目録、2〜14頁＝大学会館 E-1〜13、15頁＝昇降機設備工事仕様書、16〜24頁＝キャンパスヤード E-1〜9、25〜26頁＝追加（防犯ブザー・外灯）、27・32頁＝文学部研究棟（70-82A076）の屋外灯、28〜31・33〜35頁＝系統図・参考図など（一部は図面名が読み取れない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>★＝食堂（1階）・厨房まわりで特に見る図面。図面番号は図枠（機械は MP/MA 番号と「M○」の印の両方）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>PDF頁</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>図面番号</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>図面名</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>縮尺</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>棟</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>主な内容（食堂・厨房まわり）</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>今回の設計図との対応</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>照合する施工図・製作図（目安）・メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>（目録）</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>機械 目録</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>M1〜M26 の範囲だけ記載</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>MP-1（M1）</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>衛生設備工事特記仕様書</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>衛生の仕様</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>機 01-01〜03</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>MP-2（M2）</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>衛生設備 機器表・器具表</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>衛生機器・器具</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>機 04-01</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>MP-3（M3）</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>衛生設備 B1階平面図・系統図</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>地下1階の衛生</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>機 05-01</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>MP-4（M4）</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>衛生設備 1,2,3,屋階平面図</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>1階（食堂・厨房）の給排水配管</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>機 04-01</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>仕上-1、三友-16、意 1-23 詳細19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>MP-5（M5）</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>衛生設備 厨房配管図</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>厨房の給排水・ガス配管（詳細）</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>機 04-01</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>厨房まわり（参考）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>MP-6（M6）</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>消火設備 屋内消火栓系統図</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>屋内消火栓</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>MP-7（M7）</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>消火設備 泡消火設備系統図</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>泡消火</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>MP-8（M8）</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>消火設備 スプリンクラー設備系統図</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>スプリンクラー</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>天井改修時に要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>MP-9（M9）</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>消火設備 B1階平面図</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>地下1階の消火</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>MP-10（M10）</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>消火設備 1,2,3,屋階平面図</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>1階（食堂）の消火設備（消火栓・ヘッド）</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr"/>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>仕上-2（天井内の配管）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>MP-11（M11）</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>衛生設備 厨房器具</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>厨房器具</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>（参考）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>MP-12（M12）</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>衛生設備 厨房器具</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>厨房器具</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>（参考）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>MP-13（M13）</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>衛生設備 1階平面図（キャンパスヤード）</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>MP-14（M14）</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>衛生設備 B1階平面図（キャンパスヤード）</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>MP-15（M15）</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>衛生設備 屋内消火栓設備系統図・計算書（キャンパスヤード）</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>MP-16（M16）</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>衛生設備 消火設備系統図・計算書（キャンパスヤード）</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>MP-17（M17）</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>衛生設備 消火設備系統図（キャンパスヤード）</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>MP-51（M18）</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>衛生設備 噴水設備</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>噴水</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>MA-1（M19）</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>空気調和設備工事特記仕様書</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>空調の仕様</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>機 01-01〜03</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>MA-2（M20）</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>空気調和設備 機器表</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr"/>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>空調機器（食堂系統の空調機・ファン）</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>機 02-01</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>MA-3（M21）</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>空気調和設備 機器表</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>空調機器</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>機 02-01</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>MA-4（M22）</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>空気調和設備 系統図・詳細図</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>空調の系統・詳細</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>機 02-01・03-01</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>MA-5（M23）</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>空気調和設備 B1,1,2,3,屋階平面図</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>各階の空調配管・ダクト</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>機 02-01</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>MA-6（M24）</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>空気調和設備 1階・2階平面図</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>1階（食堂・厨房）と2階のダクト・吹出口・吸込口の配置と風量</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>機 03-01</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>仕上-2、三友-8・15・18〜21、MIDIC-1（天井内のダクト・吹出口との取合い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>MA-51（M25）</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>（機器配管外構図）</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>外構の配管</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>図面名は一部読み取り</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>MA-52（M26）</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>オイルタンク室詳細図（新設）・オイルタンク廻り詳細図</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>1/50・1/30</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>オイルタンク</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>機械</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>返却コーナー改造プラン</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>食器返却コーナーの改造（61・11・1、竣工後の改造）</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr"/>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>三友-16、MIDIC-3（返却口まわり）、目録に無い後の改造図</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>（目録）</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>電気 目録</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>E-1〜13、キャンパスヤード E-1〜9、追加など</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>E-1</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>電気設備工事特記仕様書</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>電気の仕様</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>電 -01・02</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>E-2</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>屋外電気設備図</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>1:500</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>屋外</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>電 -04</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>E-3</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>変電設備図</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>変電設備</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>電 -05</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>E-4</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>照明器具姿図・系統図</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>既存の照明器具（食堂のシャンデリア等）</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>電 -10・11</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>仕上-2、三友-20・21</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>E-5</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>動力制御盤表</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>動力盤</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>電 -05</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>E-6</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>分電盤表</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>分電盤（食堂系統の回路）</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>電 -09</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>E-7</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>動力幹線設備図</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>幹線（食堂・厨房の動力）</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>電 -05〜08</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>E-8</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>電灯コンセント設備図</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>1階（食堂）ほかの照明・コンセントの配置</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>電 -08・12</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>仕上-1・2、三友-7・11・12・16（壁・カウンター内のコンセント）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>E-9</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>自動火災報知設備図・防排煙設備図</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>自火報（系統）</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>電 -15・16</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>仕上-2（感知器の位置）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>E-10</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>自動火災報知設備図・防排煙設備図</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>自火報（平面）</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>電 -16</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>仕上-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>E-11</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>自動火災報知設備図・防排煙設備図</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>自火報（平面）</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>電 -16</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>E-12</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>自動火災報知設備図・防排煙設備図</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>自火報（平面）</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>電 -16</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>E-13</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>電灯コンセント設備図・動力設備図</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>厨房まわりの電灯・コンセント・動力（詳細）</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>電 -08</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>（厨房まわり）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>昇降機設備工事仕様書</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>昇降機</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>目録に無い</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>E-1（ヤード）</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>電気設備工事特記仕様書</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>E-2（ヤード）</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>分電盤結線図・動力制御盤表</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr"/>
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>E-3（ヤード）</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>動力幹線設備図</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr"/>
+      <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>E-4（ヤード）</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>動力幹線設備図</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>E-5（ヤード）</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>照明器具姿図・電灯設備図</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr"/>
+      <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>E-6（ヤード）</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>電灯コンセント設備図</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr"/>
+      <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>E-7（ヤード）</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>自動火災報知設備系統図</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr"/>
+      <c r="I56" s="5" t="inlineStr"/>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>E-8（ヤード）</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>自動火災報知設備図</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>1:500</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr"/>
+      <c r="I57" s="5" t="inlineStr"/>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>E-9（ヤード）</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>自動火災報知設備図</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>キャンパスヤード</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr"/>
+      <c r="I58" s="5" t="inlineStr"/>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>追1 E-1</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>防犯ブザー設備</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>防犯ブザー（60・3・13 追加）</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>追2 E-2</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>外灯設備図</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>外構</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>外灯</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>電 -04</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>E-1</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>屋外灯設備図（文学部研究棟 70-82A076）</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>別工事</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>屋外灯</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>E-1'</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>幹線系統図・弱電幹線系統図</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>幹線・弱電の系統</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>電 -05</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>E-2'</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>弱電系統図</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>大学会館</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>弱電（放送など）</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>電 -13</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>噴水動力設備</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>1:200</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>外構</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>噴水</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr"/>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>E-1</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>（図面名なし。「参考図」の印）</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr"/>
+      <c r="G65" s="5" t="inlineStr"/>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>電気室まわりの平面・単線結線（参考図）</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr"/>
+      <c r="J65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>E-1'</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>屋外灯設備図（文学部研究棟 70-82A076）</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>別工事</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>屋外灯</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr"/>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>外構の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>（図面名は読み取れず）</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="5" t="inlineStr"/>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>敷地全体の配置（かすれ）</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr"/>
+      <c r="J67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>（図面名は読み取れず）</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="5" t="inlineStr"/>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>敷地・配線ルート</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr"/>
+      <c r="J68" s="5" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>電気</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>（図面名は読み取れず）</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr"/>
+      <c r="G69" s="5" t="inlineStr"/>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>別棟の平面</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr"/>
+      <c r="J69" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:J69"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2015 大学会館東側（1階食堂）天井耐震化工事 データ索引</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ファイル：椙山改修/参考/70_15A017_大学会館東側天井耐震化工事（2015）CAD.zip（16.8MB）。工事名「70 15A017 椙山女学園大学 星が丘キャンパス 大学会館1階東側食堂天井耐震化工事」、清水建設名古屋支店一級建築士事務所。zip 内の名前は #Uxxxx 形式で、展開時に日本語に戻した（展開物はコミットしない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>「契約図」フォルダが正式（151014送付 契約図.pdf＝A-01・A-02・S-1・M-1・E-01 の5枚、DWG は 2015/10/19）。「ボツか」は不採用案と思われる（A-02 特記仕様書（法適合確認）・A-03 特記仕様書・A-04 旧版）。直下の DWG・DXF は 5月の途中版。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>260925 作図資料の16〜19頁（A-01・A-02・M-1・E-01）は、この契約図の印刷（S-1 天井改修計画は作図資料に入っていない）。作図資料の手書きメモ「CADないのか？」→ CAD（DWG）はこの zip にある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>DWG（AutoCAD 2007/2010 形式）はこの環境では開けない（中身は同名 PDF で確認）。DXF（0512修正 A-04）は ezdxf で文字を読んだ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>注意点（既存天井＝耐震化後の下地）— 三友-8・9・20・21、MIDIC-1、仕上-2 の照合用</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>① 範囲：東側食堂 ⑤〜⑦×K〜P（27.5 m×11 m、約196 m²）、天井高 CH=7,700（3FL−1,250）。西側（喫茶・CH=2,750）は対象外。天井の上は3階床梁（3G1 450×1100、3G2/3G2A 350×700、3G5/3G5A 400×800、3G6 900×900、CG3 450×650、B2 300×550、B5 250×600）、スラブ S2 t160・S4 t120。柱は2階まで。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>② 下地の形式：吊りボルトではなく「鉄骨ブドウ棚」。3階梁の側面に受材取付 B.PL-9×220×190 @3000 を、エポキシ樹脂アンカー 2-M16（D.N.締め）＋無収縮モルタル（Fc=30）で固定 → 端部受材（溝形鋼 [-150×75×6.5×10 SS400、G.PL-6 HTB 2-M16 S10T）→ 天井下地材（リップ溝形鋼 @910、ルーズホール 18φ×40 でレベル調整）。その下に LGS 野縁（19型、L-40×40 下地）を落下防止ワイヤー付きで固定し、GB-R t12.5＋岩綿吸音板（リブ t19／t9 貼分け）。天井と壁の間は EXP.J、耐震クリップ軽量下地を併用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>③ 図面の中で寸法が食い違う（要確認）：天井下地材は S-1 の伏図・A部拡大図で C-100×50×20×2.3、S-1 の取合詳細・A-02 の B部断面で C-150×50×20×3.2（SSC400）。端部受材は [-150×75×6.5×10 と L-150×75×6.5×10、ボルトは HTB（S10T）と普通ボルトの表記がある。5月の途中版（DXF）は C-100×50×20×2.3。→ 実際に入っている部材は現地で確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>④ 照明BOX：スチール t1.6 曲加工 SOP、W300×D150×L5500、LED シーリングライト 1000型×6灯（梁下）。2020/12 に器具数変更（LED シーリングライト 24台 取付高さ 7.7 m、壁ブラケット 3 m など。照度分布図で平均 605 lx）。→ 三友-20・21（照明ボックススチールパネル）、仕上-2 の照合用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>⑤ 今回の改修で下地鉄骨・吊りを足すときは、2015 のアンカー（B.PL @3000、2-M16）・ブドウ棚と干渉しないか、撤去するのか残すのかを確認。3階梁は PC 梁（PG1）の可能性があり（「既存躯体」シートの注意点④）、梁側面への追加アンカーは構造（平山さん）と協議。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>フォルダ</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>ファイル名</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>種類</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>中身</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>今回の工事との関係・メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>契約図</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>151014送付　契約図.pdf</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>2015/10/14</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>契約図5枚：A-01 建物概要表、A-02 天井伏図・断面詳細図・展開図、S-1 天井改修計画、M-1 空調設備、E-01 電灯・火報・非常放送設備平面図</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>正式。作図資料16〜19頁と同じ（S-1 を除く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>契約図</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>A-01_建物概要表 Model (1).pdf</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>2015/10/14</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>建物概要・工事項目（天井・照明LED化・スピーカー更新など）</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>作図資料16頁</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>契約図</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>A-04_天伏・断詳・展開 平・断・展開図 (1).pdf</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>2015/10/14</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>図枠は A-02「天井伏図・断面詳細図・展開図」。現況・改修後の天井伏、A-A 断面、展開、B部断面詳細</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>作図資料17頁。注意点②③④</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>契約図</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>S01_天井改修計画 Model (1).pdf</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>2015/10/14</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>S-1 東側食堂天井改修計画：天井下地材伏図（既存3階床梁伏図）、既存部材断面表、荷重条件、天井下地材取合詳細 1:20、A部拡大図 1:5</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>作図資料に無い。注意点①②③</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>契約図</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>M-01_空調設備　機器表・系統図・平面図 平・断・展開図 (1).pdf</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>2015/10/14</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>空調の機器表・系統図・平面（ファン・ダクト・吹出口の更新）</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>作図資料18頁。機 02-01・03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>契約図</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>電灯・火報・非常放送設備平面図 平・断・展開図 (1).pdf</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>2015/10/14</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>電灯・自火報・非常放送の平面</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>作図資料19頁。電 -12・14・16</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>契約図/01_A</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>A-01_建物概要表.dwg</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>DWG</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>2015/10/19</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>A-01 の CAD</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>契約図/01_A</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>A-04_天伏・断詳・展開.dwg</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>DWG</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>2015/10/19</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>A-02（天井伏・断面詳細・展開）の CAD</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>仕上-2 の照合に使える</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>契約図/01_A</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>TIZU.tif</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>TIF</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>2015/05/08</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>付近見取図の画像</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>契約図/02_S</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>S01_天井改修計画.dwg</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>DWG</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>2015/10/19</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>S-1 の CAD</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>三友-8 の照合に使える</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>契約図/03_M</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>M-01_空調設備　機器表・系統図・平面図.dwg</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>DWG</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>2015/10/19</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>M-1 の CAD（外部参照フォルダに A-04 など）</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>契約図/04_E</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>電灯・火報・非常放送設備平面図.dwg</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>DWG</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>2015/10/19</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>E-01 の CAD</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>契約図/04_E</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>20201215器具数変更　　電灯・火報・非常放送設備平面図.dwg</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>DWG</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>2020/12/15</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>2020 の照明器具数変更（AutoCAD 2010 形式）</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>注意点④</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>（直下）</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>20201214照度分布図.pdf ほか（ｘ20201211・ｘｘ照度分布図、旧…A.pdf、…1216.pdf）</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>2020/12/10〜16</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>食堂（24.3 m×10.7 m、天井高 7.7 m）の水平面照度分布。最終（1216）：LED シーリングライト NDNN57911-LZ9 24台＋LDL40 42台・LDL20 6台（取付高さ 3 m）、平均 605 lx</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>2020 の器具数変更の検討。電 -12</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>（直下）</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>椙山女学園大学　大学会館東側天井耐震化工事.sssx</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>照度計算データ</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>2020/12/16</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>照度計算ソフトのデータ</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>（直下）</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>（0512修正）A-04_天伏・断詳・展開.dwg／.dxf</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>DWG/DXF</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>2015/05〜07</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>A-04 の5月修正版（途中版）。DXF の文字：C-100×50×20×2.3@910（SSC400）、EXP.J、耐震クリップ軽量下地併用</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>注意点③</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>（直下）</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>A-01_建物概要表.dwg、A1WAKU.dwg、A1LOGO(社内限).dwg、TIZU.tif</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>DWG/TIF</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>2015/05〜06</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>途中版・図枠・ロゴ</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>（直下）/02_S</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>S01_天井改修計画.dwg／S01_天井改修計画 (1).xdw</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>DWG/XDW</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>2015/06/09（xdw は 2026/05/28 印刷）</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>S-1 の途中版。xdw は DocuWorks 印刷（plot.log に 2026/05/28 の印刷記録）</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>（直下）/02_S</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>0513_意匠図.xdw</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>XDW</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>2015/05/13</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>意匠図（DocuWorks。この環境では開けない）</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>（直下）/02_S</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>村上部長スケッチ.pdf</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>PDF（スキャン）</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>2015/05/13</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>天井下地材伏図の手書きスケッチ（構造の検討メモ）</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ボツか</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>A-02 特記仕様書（法適合確認）.dwg</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>DWG</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>2015/05/08</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>特記仕様書（法適合確認）</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>不採用案と思われる</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>ボツか</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>A-03_特記仕様書.xlsm</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>XLSM</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>2015/05/08</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>建築特記仕様書の作成マクロ（シート：利用方法、建築特記仕様書01、仕様書1〜30）</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>不採用案と思われる</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>ボツか</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>A-04_天伏・断詳・展開.dwg</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>DWG</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>2015/05/11</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>A-04 の旧版</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>不採用案と思われる</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A14:F37"/>
+  <mergeCells count="5">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A8:H8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/椙山改修/チェック/設計図_索引.xlsx
+++ b/椙山改修/チェック/設計図_索引.xlsx
@@ -2515,14 +2515,14 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>④ PG1 の位置：2015 天井耐震化工事の S-1（既存3階床梁伏図）では、東側食堂（⑤〜⑦×K〜P、天井高 CH=7,700）の上は3階床梁（3G1 450×1100 など）で、柱は2階までと注記されている。食堂の上の3階床梁が PC の長スパン梁（PG1）である可能性が高い（S-5 3階床伏図で要確認）。2015 の天井下地（ブドウ棚）は、この3階梁の側面に B.PL＋エポキシ樹脂アンカー 2-M16 で取り付けてあり、特記に「大梁のスターラップを切断しないよう探査のうえ施工」とある。今回の三友-8・9・20・21・MIDIC-1 の取付けも同じ梁になるので、PC鋼材・既存アンカーの位置に特に注意。</t>
+          <t>④ PG1 の位置：2015 天井耐震化工事の S-1（既存3階床梁伏図）では、東側食堂の上は3階床梁（3G1 450×1100 など）で、柱は2階までと注記されている。食堂の上の3階床梁が PC の長スパン梁（PG1、③〜⑦通り）である可能性が高い（S-5 3階床伏図で要確認）。今回の三友の下地鉄骨・MIDIC-1 などを3階梁に取り付ける場合は、PC鋼材の位置に特に注意し、構造（平山さん）と協議。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>⑤ 既存躯体は昭和60年竣工（築40年）。アンカーの施工試験（引張試験）を計-4 で計画に入れること。2015 天井耐震化工事で既に打たれたアンカー・吊りボルトの位置（②の A-02）との干渉にも注意。</t>
+          <t>⑤ 既存躯体は昭和60年竣工（築40年）。アンカーの施工試験（引張試験）を計-4 で計画に入れること。</t>
         </is>
       </c>
     </row>
@@ -4616,19 +4616,15 @@
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
-          <t>2015 改修時の天井伏・天井断面詳細・展開（既存の天井下地・吊りボルト）</t>
+          <t>2015 改修時の天井伏・天井断面詳細・展開（既存の天井下地）</t>
         </is>
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>仕上-2・3・4、三友-8、計-4</t>
-        </is>
-      </c>
-      <c r="K55" s="9" t="inlineStr">
-        <is>
-          <t>注意点⑤</t>
-        </is>
-      </c>
+          <t>参考（2015 の範囲は今回と重ならない）</t>
+        </is>
+      </c>
+      <c r="K55" s="9" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -9834,42 +9830,42 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>注意点（既存天井＝耐震化後の下地）— 三友-8・9・20・21、MIDIC-1、仕上-2 の照合用</t>
+          <t>注意点（既存天井＝耐震化後の下地）— 2015 の施工範囲は今回の施工範囲と重ならないので参考（10/31 小山さん確認）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>① 範囲：東側食堂 ⑤〜⑦×K〜P（27.5 m×11 m、約196 m²）、天井高 CH=7,700（3FL−1,250）。西側（喫茶・CH=2,750）は対象外。天井の上は3階床梁（3G1 450×1100、3G2/3G2A 350×700、3G5/3G5A 400×800、3G6 900×900、CG3 450×650、B2 300×550、B5 250×600）、スラブ S2 t160・S4 t120。柱は2階まで。</t>
+          <t>① 範囲：東側食堂 ⑤〜⑦×K〜P（27.5 m×11 m、約196 m²）、天井高 CH=7,700（3FL−1,250）。西側（喫茶・CH=2,750）は対象外。天井の上は3階床梁（3G1 450×1100、3G2/3G2A 350×700、3G5/3G5A 400×800、3G6 900×900、CG3 450×650、B2 300×550、B5 250×600）、スラブ S2 t160・S4 t120。柱は2階まで。→ 今回の施工範囲と重ならないので参考。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="52" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>② 下地の形式：吊りボルトではなく「鉄骨ブドウ棚」。3階梁の側面に受材取付 B.PL-9×220×190 @3000 を、エポキシ樹脂アンカー 2-M16（D.N.締め）＋無収縮モルタル（Fc=30）で固定 → 端部受材（溝形鋼 [-150×75×6.5×10 SS400、G.PL-6 HTB 2-M16 S10T）→ 天井下地材（リップ溝形鋼 @910、ルーズホール 18φ×40 でレベル調整）。その下に LGS 野縁（19型、L-40×40 下地）を落下防止ワイヤー付きで固定し、GB-R t12.5＋岩綿吸音板（リブ t19／t9 貼分け）。天井と壁の間は EXP.J、耐震クリップ軽量下地を併用。</t>
+          <t>② 下地の形式：吊りボルトではなく「鉄骨ブドウ棚」。3階梁の側面に受材取付 B.PL-9×220×190 @3000 を、エポキシ樹脂アンカー 2-M16（D.N.締め）＋無収縮モルタル（Fc=30）で固定 → 端部受材（溝形鋼 [-150×75×6.5×10 SS400、G.PL-6 HTB 2-M16 S10T）→ 天井下地材（リップ溝形鋼 @910、ルーズホール 18φ×40 でレベル調整）。その下に LGS 野縁（19型、L-40×40 下地）を落下防止ワイヤー付きで固定し、GB-R t12.5＋岩綿吸音板（リブ t19／t9 貼分け）。天井と壁の間は EXP.J、耐震クリップ軽量下地を併用。→ 参考。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>③ 図面の中で寸法が食い違う（要確認）：天井下地材は S-1 の伏図・A部拡大図で C-100×50×20×2.3、S-1 の取合詳細・A-02 の B部断面で C-150×50×20×3.2（SSC400）。端部受材は [-150×75×6.5×10 と L-150×75×6.5×10、ボルトは HTB（S10T）と普通ボルトの表記がある。5月の途中版（DXF）は C-100×50×20×2.3。→ 実際に入っている部材は現地で確認。</t>
+          <t>③ 図面の中で部材寸法の表記が食い違う（天井下地材 C-100×50×20×2.3／C-150×50×20×3.2、端部受材［／L、HTB／普通ボルト）。→ 今回の施工範囲と重ならないため確認不要（10/31 小山さん確認）。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>④ 照明BOX：スチール t1.6 曲加工 SOP、W300×D150×L5500、LED シーリングライト 1000型×6灯（梁下）。2020/12 に器具数変更（LED シーリングライト 24台 取付高さ 7.7 m、壁ブラケット 3 m など。照度分布図で平均 605 lx）。→ 三友-20・21（照明ボックススチールパネル）、仕上-2 の照合用。</t>
+          <t>④ 照明BOX：スチール t1.6 曲加工 SOP、W300×D150×L5500、LED シーリングライト 1000型×6灯（梁下）。2020/12 に器具数変更（LED シーリングライト 24台 取付高さ 7.7 m、壁ブラケット 3 m など。照度分布図で平均 605 lx）。→ 範囲が重ならないので参考（三友-20・21・仕上-2 を見るときの参考程度）。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>⑤ 今回の改修で下地鉄骨・吊りを足すときは、2015 のアンカー（B.PL @3000、2-M16）・ブドウ棚と干渉しないか、撤去するのか残すのかを確認。3階梁は PC 梁（PG1）の可能性があり（「既存躯体」シートの注意点④）、梁側面への追加アンカーは構造（平山さん）と協議。</t>
+          <t>⑤ PC梁 PG1 とあと施工アンカーの注意は「既存躯体」シートの注意点③④を見る（2015 範囲とは重ならない）。</t>
         </is>
       </c>
     </row>
@@ -9997,7 +9993,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>作図資料17頁。注意点②③④</t>
+          <t>作図資料17頁。参考</t>
         </is>
       </c>
     </row>
@@ -10029,7 +10025,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>作図資料に無い。注意点①②③</t>
+          <t>作図資料に無い。参考</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10149,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>仕上-2 の照合に使える</t>
+          <t>参考（範囲が重ならない）</t>
         </is>
       </c>
     </row>
@@ -10213,7 +10209,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>三友-8 の照合に使える</t>
+          <t>参考（範囲が重ならない）</t>
         </is>
       </c>
     </row>
@@ -10301,7 +10297,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>注意点④</t>
+          <t>参考</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10389,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>注意点③</t>
+          <t>参考</t>
         </is>
       </c>
     </row>
